--- a/static/data/exports/Retro_HP_GE_2009.xlsx
+++ b/static/data/exports/Retro_HP_GE_2009.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="Q3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>6</v>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="Q18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>6</v>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="Q29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>6</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Q39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>6</v>
@@ -3491,7 +3491,7 @@
         </is>
       </c>
       <c r="Q49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
         <v>6</v>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="Q59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
         <v>6</v>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="Q69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
         <v>6</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="Q78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
         <v>6</v>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
         <v>6</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="Q96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" t="n">
         <v>6</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="Q105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" t="n">
         <v>6</v>
@@ -7583,7 +7583,7 @@
         </is>
       </c>
       <c r="Q115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
         <v>6</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="Q125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
         <v>6</v>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="Q134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" t="n">
         <v>6</v>
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="Q144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" t="n">
         <v>6</v>
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="Q155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" t="n">
         <v>6</v>
@@ -10621,7 +10621,7 @@
         </is>
       </c>
       <c r="Q164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R164" t="n">
         <v>6</v>
@@ -11241,7 +11241,7 @@
         </is>
       </c>
       <c r="Q174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R174" t="n">
         <v>6</v>
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="Q185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R185" t="n">
         <v>6</v>
@@ -16573,7 +16573,7 @@
         </is>
       </c>
       <c r="Q260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R260" t="n">
         <v>6</v>
@@ -18185,7 +18185,7 @@
         </is>
       </c>
       <c r="Q286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R286" t="n">
         <v>6</v>
@@ -18681,7 +18681,7 @@
         </is>
       </c>
       <c r="Q294" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R294" t="n">
         <v>6</v>
@@ -19177,7 +19177,7 @@
         </is>
       </c>
       <c r="Q302" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R302" t="n">
         <v>6</v>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="Q310" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R310" t="n">
         <v>6</v>
@@ -20169,7 +20169,7 @@
         </is>
       </c>
       <c r="Q318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R318" t="n">
         <v>6</v>
@@ -20665,7 +20665,7 @@
         </is>
       </c>
       <c r="Q326" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R326" t="n">
         <v>6</v>
@@ -21223,7 +21223,7 @@
         </is>
       </c>
       <c r="Q335" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R335" t="n">
         <v>6</v>
@@ -21719,7 +21719,7 @@
         </is>
       </c>
       <c r="Q343" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R343" t="n">
         <v>6</v>
@@ -22153,7 +22153,7 @@
         </is>
       </c>
       <c r="Q350" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R350" t="n">
         <v>6</v>
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="Q358" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R358" t="n">
         <v>6</v>
@@ -23145,7 +23145,7 @@
         </is>
       </c>
       <c r="Q366" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R366" t="n">
         <v>6</v>
@@ -23703,7 +23703,7 @@
         </is>
       </c>
       <c r="Q375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R375" t="n">
         <v>6</v>
@@ -24137,7 +24137,7 @@
         </is>
       </c>
       <c r="Q382" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R382" t="n">
         <v>6</v>
@@ -24633,7 +24633,7 @@
         </is>
       </c>
       <c r="Q390" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R390" t="n">
         <v>6</v>
@@ -24959,20 +24959,20 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1508961</v>
+        <v>1508960</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>MALKIAT SINGH</t>
+          <t>PANKAJ KATNA</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>RRD</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="D396" t="n">
-        <v>16564</v>
+        <v>16539</v>
       </c>
       <c r="E396" t="n">
         <v>63</v>
@@ -24996,12 +24996,12 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>MALKIAT SINGH</t>
+          <t>PANKAJ KATNA</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>RRD</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="Q396" t="b">
@@ -25021,20 +25021,20 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1508960</v>
+        <v>1508961</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PANKAJ KATNA</t>
+          <t>MALKIAT SINGH</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>RRD</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>16539</v>
+        <v>16564</v>
       </c>
       <c r="E397" t="n">
         <v>63</v>
@@ -25058,12 +25058,12 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>PANKAJ KATNA</t>
+          <t>MALKIAT SINGH</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>RRD</t>
         </is>
       </c>
       <c r="Q397" t="b">
@@ -25191,7 +25191,7 @@
         </is>
       </c>
       <c r="Q399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R399" t="n">
         <v>6</v>
@@ -25625,7 +25625,7 @@
         </is>
       </c>
       <c r="Q406" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R406" t="n">
         <v>6</v>
@@ -26059,7 +26059,7 @@
         </is>
       </c>
       <c r="Q413" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R413" t="n">
         <v>6</v>
@@ -26493,7 +26493,7 @@
         </is>
       </c>
       <c r="Q420" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R420" t="n">
         <v>6</v>
@@ -26695,20 +26695,20 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1509138</v>
+        <v>1509139</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>GURNAM SINGH CHANDEL</t>
+          <t>BRIJ LAL</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>16542</v>
+        <v>16539</v>
       </c>
       <c r="E424" t="n">
         <v>45</v>
@@ -26732,12 +26732,12 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>GURNAM SINGH CHANDEL</t>
+          <t>BRIJ LAL</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="Q424" t="b">
@@ -26757,20 +26757,20 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1509139</v>
+        <v>1509138</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>BRIJ LAL</t>
+          <t>GURNAM SINGH CHANDEL</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>16539</v>
+        <v>16542</v>
       </c>
       <c r="E425" t="n">
         <v>45</v>
@@ -26794,12 +26794,12 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>BRIJ LAL</t>
+          <t>GURNAM SINGH CHANDEL</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="Q425" t="b">
@@ -26927,7 +26927,7 @@
         </is>
       </c>
       <c r="Q427" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R427" t="n">
         <v>6</v>
@@ -27361,7 +27361,7 @@
         </is>
       </c>
       <c r="Q434" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R434" t="n">
         <v>6</v>
@@ -27795,7 +27795,7 @@
         </is>
       </c>
       <c r="Q441" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R441" t="n">
         <v>6</v>
@@ -28229,7 +28229,7 @@
         </is>
       </c>
       <c r="Q448" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R448" t="n">
         <v>6</v>
@@ -28663,7 +28663,7 @@
         </is>
       </c>
       <c r="Q455" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R455" t="n">
         <v>6</v>
@@ -29097,7 +29097,7 @@
         </is>
       </c>
       <c r="Q462" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R462" t="n">
         <v>6</v>
@@ -29531,7 +29531,7 @@
         </is>
       </c>
       <c r="Q469" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R469" t="n">
         <v>6</v>
@@ -29965,7 +29965,7 @@
         </is>
       </c>
       <c r="Q476" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R476" t="n">
         <v>6</v>
@@ -30399,7 +30399,7 @@
         </is>
       </c>
       <c r="Q483" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R483" t="n">
         <v>6</v>
@@ -30771,7 +30771,7 @@
         </is>
       </c>
       <c r="Q489" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R489" t="n">
         <v>6</v>
@@ -31205,7 +31205,7 @@
         </is>
       </c>
       <c r="Q496" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R496" t="n">
         <v>6</v>
@@ -31701,7 +31701,7 @@
         </is>
       </c>
       <c r="Q504" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R504" t="n">
         <v>6</v>
@@ -32445,7 +32445,7 @@
         </is>
       </c>
       <c r="Q516" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R516" t="n">
         <v>6</v>

--- a/static/data/exports/Retro_HP_GE_2009.xlsx
+++ b/static/data/exports/Retro_HP_GE_2009.xlsx
@@ -1284,11 +1284,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E14" t="n">
         <v>846</v>
@@ -2577,20 +2577,20 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1506216</v>
+        <v>1506215</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NIRMLA SHARMA</t>
+          <t>JOGINDER SINGH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>16538</v>
+        <v>16539</v>
       </c>
       <c r="E35" t="n">
         <v>85</v>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>NIRMLA SHARMA</t>
+          <t>JOGINDER SINGH</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="Q35" t="b">
@@ -2639,20 +2639,20 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1506215</v>
+        <v>1506216</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JOGINDER SINGH</t>
+          <t>NIRMLA SHARMA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16539</v>
+        <v>16538</v>
       </c>
       <c r="E36" t="n">
         <v>85</v>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>JOGINDER SINGH</t>
+          <t>NIRMLA SHARMA</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="Q36" t="b">
@@ -12568,11 +12568,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E196" t="n">
         <v>238</v>
@@ -12940,11 +12940,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E202" t="n">
         <v>824</v>
@@ -13312,11 +13312,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E208" t="n">
         <v>820</v>
@@ -13684,11 +13684,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E214" t="n">
         <v>1283</v>
@@ -14056,11 +14056,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E220" t="n">
         <v>4706</v>
@@ -14428,11 +14428,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E226" t="n">
         <v>1685</v>
@@ -14800,11 +14800,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E232" t="n">
         <v>778</v>
@@ -15172,11 +15172,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E238" t="n">
         <v>924</v>
@@ -15544,11 +15544,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E244" t="n">
         <v>1219</v>
@@ -15916,11 +15916,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E250" t="n">
         <v>675</v>
@@ -16288,11 +16288,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E256" t="n">
         <v>1278</v>
@@ -17156,11 +17156,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E270" t="n">
         <v>793</v>
@@ -17528,11 +17528,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E276" t="n">
         <v>1029</v>
@@ -17900,11 +17900,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E282" t="n">
         <v>776</v>
@@ -24463,20 +24463,20 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1508905</v>
+        <v>1508904</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>RAJ KUMAR</t>
+          <t>MALKIAT SINGH</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>RRD</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>16538</v>
+        <v>16564</v>
       </c>
       <c r="E388" t="n">
         <v>63</v>
@@ -24500,12 +24500,12 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>RAJ KUMAR</t>
+          <t>MALKIAT SINGH</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>RWS</t>
+          <t>RRD</t>
         </is>
       </c>
       <c r="Q388" t="b">
@@ -24525,20 +24525,20 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1508904</v>
+        <v>1508905</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MALKIAT SINGH</t>
+          <t>RAJ KUMAR</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>RRD</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>16564</v>
+        <v>16538</v>
       </c>
       <c r="E389" t="n">
         <v>63</v>
@@ -24562,12 +24562,12 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>MALKIAT SINGH</t>
+          <t>RAJ KUMAR</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>RRD</t>
+          <t>RWS</t>
         </is>
       </c>
       <c r="Q389" t="b">
@@ -26695,20 +26695,20 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1509139</v>
+        <v>1509138</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>BRIJ LAL</t>
+          <t>GURNAM SINGH CHANDEL</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>16539</v>
+        <v>16542</v>
       </c>
       <c r="E424" t="n">
         <v>45</v>
@@ -26732,12 +26732,12 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>BRIJ LAL</t>
+          <t>GURNAM SINGH CHANDEL</t>
         </is>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="Q424" t="b">
@@ -26757,20 +26757,20 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>1509138</v>
+        <v>1509139</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>GURNAM SINGH CHANDEL</t>
+          <t>BRIJ LAL</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>16542</v>
+        <v>16539</v>
       </c>
       <c r="E425" t="n">
         <v>45</v>
@@ -26794,12 +26794,12 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>GURNAM SINGH CHANDEL</t>
+          <t>BRIJ LAL</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="Q425" t="b">
@@ -32160,11 +32160,11 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E512" t="n">
         <v>1712</v>
@@ -32966,11 +32966,11 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E525" t="n">
         <v>1075</v>
